--- a/2026/2DE MAYO/Junio/2DEDMAYO-Mayo.xlsx
+++ b/2026/2DE MAYO/Junio/2DEDMAYO-Mayo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\2DE MAYO\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\2DE MAYO\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82BEE972-BCAD-4CD2-8742-A6CDFD29945D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A755A18-DD2C-48C8-8B58-EBD1D57FFD30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,19 +19,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$36</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$108</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$107</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="142">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -129,9 +124,6 @@
     <t>ADMINISTRADORA: CAROLINA CANCIANI MP:1148</t>
   </si>
   <si>
-    <t>SAC</t>
-  </si>
-  <si>
     <t>GASTOS EXTRAORDINARIOS CON PREVISION:</t>
   </si>
   <si>
@@ -414,18 +406,12 @@
     <t>Gustavo Padron - Sr. Contador</t>
   </si>
   <si>
-    <t>Transf 07/05</t>
-  </si>
-  <si>
     <t>Transf 05/05</t>
   </si>
   <si>
     <t>Transf 08/05</t>
   </si>
   <si>
-    <t>Servicios Sarcinelli - Trabajos en cambios de sensores de movimientos en palier</t>
-  </si>
-  <si>
     <t>Transf 12/05</t>
   </si>
   <si>
@@ -450,10 +436,22 @@
     <t>Julio Doartero - Reparacion de techo baño y balcon  7A</t>
   </si>
   <si>
-    <t>Servicios Sarcinelli - Trabajos en cambios de sensores de movimientos en palier 3er piso</t>
-  </si>
-  <si>
-    <t>Honorarios administracion  - Se adeudan</t>
+    <t>Honorarios administracion  - Mayo</t>
+  </si>
+  <si>
+    <t>Reemplazo</t>
+  </si>
+  <si>
+    <t>Compra de materiales: hierro, cemento, bolsas de arena, bolsas de pieda y alambre de fardo</t>
+  </si>
+  <si>
+    <t>Transf 02/06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lamparas </t>
+  </si>
+  <si>
+    <t>Transf 05/06</t>
   </si>
 </sst>
 </file>
@@ -1209,7 +1207,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="213">
+  <cellXfs count="217">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1421,7 +1419,6 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="22" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="22" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="7" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1444,12 +1441,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="44" fontId="15" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="16" fontId="18" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1459,18 +1482,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1495,6 +1506,72 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1509,12 +1586,6 @@
     </xf>
     <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1524,83 +1595,18 @@
     <xf numFmtId="0" fontId="20" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="8" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="15" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1679,9 +1685,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1719,9 +1725,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1754,26 +1760,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1806,26 +1795,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1999,31 +1971,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M112"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M111"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14"/>
-      <c r="B1" s="160" t="s">
-        <v>108</v>
-      </c>
-      <c r="C1" s="160"/>
-      <c r="D1" s="160"/>
+      <c r="B1" s="171" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
       <c r="E1" s="51"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="15"/>
       <c r="B2" s="52" t="s">
         <v>22</v>
@@ -2032,16 +2004,16 @@
       <c r="D2" s="52"/>
       <c r="E2" s="53"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15"/>
-      <c r="B3" s="165" t="s">
-        <v>97</v>
-      </c>
-      <c r="C3" s="165"/>
-      <c r="D3" s="165"/>
-      <c r="E3" s="166"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="172" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="172"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="173"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="18" t="s">
         <v>0</v>
       </c>
@@ -2052,12 +2024,12 @@
       <c r="D4" s="19"/>
       <c r="E4" s="20"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="52" t="s">
@@ -2065,68 +2037,68 @@
       </c>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
       <c r="D6" s="19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E6" s="20"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="168" t="s">
-        <v>120</v>
-      </c>
-      <c r="C8" s="168"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="168"/>
-      <c r="C9" s="168"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="168"/>
-      <c r="C10" s="168"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="167" t="s">
-        <v>88</v>
-      </c>
-      <c r="B13" s="167"/>
-      <c r="C13" s="167"/>
-      <c r="D13" s="167"/>
-      <c r="E13" s="167"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="167"/>
-      <c r="B14" s="167"/>
-      <c r="C14" s="167"/>
-      <c r="D14" s="167"/>
-      <c r="E14" s="167"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="167"/>
-      <c r="B15" s="167"/>
-      <c r="C15" s="167"/>
-      <c r="D15" s="167"/>
-      <c r="E15" s="167"/>
-    </row>
-    <row r="16" spans="1:5" ht="127.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="167"/>
-      <c r="B16" s="167"/>
-      <c r="C16" s="167"/>
-      <c r="D16" s="167"/>
-      <c r="E16" s="167"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="175" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" s="175"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="175"/>
+      <c r="C9" s="175"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="175"/>
+      <c r="C10" s="175"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="174" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" s="174"/>
+      <c r="C13" s="174"/>
+      <c r="D13" s="174"/>
+      <c r="E13" s="174"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="174"/>
+      <c r="B14" s="174"/>
+      <c r="C14" s="174"/>
+      <c r="D14" s="174"/>
+      <c r="E14" s="174"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="174"/>
+      <c r="B15" s="174"/>
+      <c r="C15" s="174"/>
+      <c r="D15" s="174"/>
+      <c r="E15" s="174"/>
+    </row>
+    <row r="16" spans="1:5" ht="127.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="174"/>
+      <c r="B16" s="174"/>
+      <c r="C16" s="174"/>
+      <c r="D16" s="174"/>
+      <c r="E16" s="174"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
         <v>9</v>
       </c>
@@ -2135,7 +2107,7 @@
       <c r="D20" s="8"/>
       <c r="E20" s="13"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="27" t="s">
         <v>27</v>
       </c>
@@ -2144,42 +2116,42 @@
       <c r="D21" s="26"/>
       <c r="E21" s="26"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="141">
-        <v>1217885.55</v>
+        <v>1899703.78</v>
       </c>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="141">
-        <v>-301426.69</v>
+        <v>-470176.69</v>
       </c>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
       <c r="D24" s="141">
-        <v>0.14000000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="44" t="s">
         <v>28</v>
       </c>
@@ -2187,645 +2159,654 @@
       <c r="C25" s="44"/>
       <c r="D25" s="142">
         <f>SUM(D22:D24)</f>
-        <v>916459.00000000012</v>
+        <v>1429528</v>
       </c>
       <c r="E25" s="89"/>
       <c r="G25" s="21"/>
     </row>
-    <row r="26" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
       <c r="D26" s="141"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="23"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
       <c r="D27" s="141"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
       <c r="D28" s="141"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="5"/>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
+        <v>137</v>
+      </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="143"/>
+      <c r="D29" s="213">
+        <v>84700</v>
+      </c>
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="143"/>
-      <c r="E30" s="5"/>
-    </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="44" t="s">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="B31" s="44"/>
-      <c r="C31" s="44"/>
-      <c r="D31" s="144">
-        <f>SUM(D26:D30)</f>
-        <v>0</v>
-      </c>
-      <c r="E31" s="89"/>
-    </row>
-    <row r="32" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="24" t="s">
+      <c r="B30" s="44"/>
+      <c r="C30" s="44"/>
+      <c r="D30" s="143">
+        <f>SUM(D26:D29)</f>
+        <v>84700</v>
+      </c>
+      <c r="E30" s="89"/>
+    </row>
+    <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B32" s="24"/>
-      <c r="C32" s="24"/>
+      <c r="B31" s="24"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="144"/>
+      <c r="E31" s="90">
+        <f>D25+D30</f>
+        <v>1514228</v>
+      </c>
+      <c r="F31" s="21"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32" s="27"/>
+      <c r="C32" s="27"/>
       <c r="D32" s="145"/>
-      <c r="E32" s="90">
-        <f>D25+D31</f>
-        <v>916459.00000000012</v>
-      </c>
-      <c r="F32" s="21"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="B33" s="27"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="146"/>
-      <c r="E33" s="91"/>
-    </row>
-    <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="163" t="s">
-        <v>126</v>
-      </c>
-      <c r="B34" s="164"/>
+      <c r="E32" s="91"/>
+    </row>
+    <row r="33" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="165" t="s">
+        <v>125</v>
+      </c>
+      <c r="B33" s="166"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="216">
+        <v>45000</v>
+      </c>
+      <c r="E33" s="92" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="165" t="s">
+        <v>136</v>
+      </c>
+      <c r="B34" s="166"/>
       <c r="C34" s="41"/>
-      <c r="D34" s="141">
-        <v>45000</v>
-      </c>
-      <c r="E34" s="92" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="163" t="s">
-        <v>140</v>
-      </c>
-      <c r="B35" s="164"/>
-      <c r="C35" s="41"/>
-      <c r="D35" s="205"/>
-      <c r="E35" s="92"/>
-    </row>
-    <row r="36" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="24" t="s">
+      <c r="D34" s="211">
+        <v>120000</v>
+      </c>
+      <c r="E34" s="92"/>
+    </row>
+    <row r="35" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="24" t="s">
         <v>15</v>
+      </c>
+      <c r="B35" s="24"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="156"/>
+      <c r="E35" s="93">
+        <f>SUM(D33:D34)</f>
+        <v>165000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="27" t="s">
+        <v>25</v>
       </c>
       <c r="B36" s="24"/>
       <c r="C36" s="24"/>
-      <c r="D36" s="206"/>
-      <c r="E36" s="93">
-        <f>SUM(D34:D35)</f>
-        <v>45000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="B37" s="24"/>
-      <c r="C37" s="24"/>
-      <c r="D37" s="207"/>
-      <c r="E37" s="94"/>
-    </row>
-    <row r="38" spans="1:7" s="30" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="169" t="s">
-        <v>96</v>
-      </c>
-      <c r="B38" s="170"/>
+      <c r="D36" s="157"/>
+      <c r="E36" s="94"/>
+    </row>
+    <row r="37" spans="1:7" s="30" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="176" t="s">
+        <v>95</v>
+      </c>
+      <c r="B37" s="177"/>
+      <c r="C37" s="42"/>
+      <c r="D37" s="167">
+        <v>65251.97</v>
+      </c>
+      <c r="E37" s="169" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="178"/>
+      <c r="B38" s="179"/>
       <c r="C38" s="42"/>
-      <c r="D38" s="208">
+      <c r="D38" s="168"/>
+      <c r="E38" s="170"/>
+    </row>
+    <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="B39" s="24"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="156"/>
+      <c r="E39" s="58">
+        <f>SUM(D37:D38)</f>
         <v>65251.97</v>
       </c>
-      <c r="E38" s="158" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="171"/>
-      <c r="B39" s="172"/>
-      <c r="C39" s="42"/>
-      <c r="D39" s="209"/>
-      <c r="E39" s="159"/>
-    </row>
-    <row r="40" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="B40" s="24"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="206"/>
-      <c r="E40" s="58">
-        <f>SUM(D38:D39)</f>
-        <v>65251.97</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="27" t="s">
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="B41" s="95"/>
-      <c r="C41" s="95"/>
-      <c r="D41" s="210"/>
-      <c r="E41" s="148"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B40" s="95"/>
+      <c r="C40" s="95"/>
+      <c r="D40" s="158"/>
+      <c r="E40" s="147"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" s="5"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="212">
+        <v>701906.85</v>
+      </c>
+      <c r="E41" s="99" t="s">
+        <v>129</v>
+      </c>
+      <c r="G41" s="77"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="5"/>
-      <c r="C42" s="41"/>
-      <c r="D42" s="147">
-        <v>646408.72</v>
+        <v>122</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C42" s="5"/>
+      <c r="D42" s="212">
+        <v>54804.85</v>
       </c>
       <c r="E42" s="99" t="s">
-        <v>132</v>
-      </c>
-      <c r="G42" s="77"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
-        <v>123</v>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="5" t="str">
+        <f>A42</f>
+        <v>Sindicatos mes de MAYO</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C43" s="5"/>
-      <c r="D43" s="147">
-        <v>50525.440000000002</v>
-      </c>
-      <c r="E43" s="99" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D43" s="212">
+        <v>101643.56</v>
+      </c>
+      <c r="E43" s="100" t="str">
+        <f>E42</f>
+        <v>Debito 13/05</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="str">
         <f>A43</f>
         <v>Sindicatos mes de MAYO</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C44" s="5"/>
-      <c r="D44" s="147">
-        <v>94598.2</v>
-      </c>
-      <c r="E44" s="100" t="str">
+      <c r="D44" s="212">
+        <v>6089.43</v>
+      </c>
+      <c r="E44" s="101" t="str">
         <f>E43</f>
         <v>Debito 13/05</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="str">
-        <f>A44</f>
-        <v>Sindicatos mes de MAYO</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C45" s="5"/>
-      <c r="D45" s="147">
-        <v>5613.94</v>
-      </c>
-      <c r="E45" s="101" t="str">
-        <f>E44</f>
-        <v>Debito 13/05</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="24" t="s">
+    <row r="45" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="24" t="s">
         <v>3</v>
+      </c>
+      <c r="B45" s="95"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="159"/>
+      <c r="E45" s="58">
+        <f>SUM(D41:D44)</f>
+        <v>864444.69000000006</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="27" t="s">
+        <v>17</v>
       </c>
       <c r="B46" s="95"/>
       <c r="C46" s="95"/>
-      <c r="D46" s="211"/>
-      <c r="E46" s="58">
-        <f>SUM(D42:D45)</f>
-        <v>797146.29999999981</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="B47" s="95"/>
-      <c r="C47" s="95"/>
-      <c r="D47" s="210"/>
-      <c r="E47" s="148"/>
-    </row>
-    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="5" t="s">
+      <c r="D46" s="158"/>
+      <c r="E46" s="147"/>
+    </row>
+    <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="212">
+        <v>371485.85</v>
+      </c>
+      <c r="E47" s="99" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="128" t="s">
         <v>92</v>
       </c>
-      <c r="B48" s="5"/>
+      <c r="B48" s="129"/>
       <c r="C48" s="5"/>
-      <c r="D48" s="147">
-        <v>362202.08</v>
+      <c r="D48" s="212">
+        <v>355959.47</v>
       </c>
       <c r="E48" s="99" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="128" t="s">
-        <v>93</v>
-      </c>
-      <c r="B49" s="129"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="147">
-        <v>345591.71</v>
-      </c>
-      <c r="E49" s="99" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="24" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="24" t="s">
         <v>4</v>
       </c>
+      <c r="B49" s="24"/>
+      <c r="C49" s="24"/>
+      <c r="D49" s="160"/>
+      <c r="E49" s="58">
+        <f>SUM(D47:D48)</f>
+        <v>727445.32</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="27"/>
       <c r="B50" s="24"/>
       <c r="C50" s="24"/>
-      <c r="D50" s="212"/>
-      <c r="E50" s="58">
-        <f>SUM(D48:D49)</f>
-        <v>707793.79</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="27"/>
-      <c r="B51" s="24"/>
-      <c r="C51" s="24"/>
-      <c r="D51" s="206"/>
-      <c r="E51" s="149"/>
-    </row>
-    <row r="52" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D50" s="156"/>
+      <c r="E50" s="148"/>
+    </row>
+    <row r="51" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="102" t="s">
+        <v>94</v>
+      </c>
+      <c r="B51" s="98"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="146">
+        <v>25141.200000000001</v>
+      </c>
+      <c r="E51" s="99" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="102" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="B52" s="98"/>
       <c r="C52" s="5"/>
-      <c r="D52" s="147">
-        <v>25141.200000000001</v>
-      </c>
-      <c r="E52" s="99" t="s">
+      <c r="D52" s="212">
+        <v>105000</v>
+      </c>
+      <c r="E52" s="137" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="161" t="s">
+        <v>138</v>
+      </c>
+      <c r="B53" s="162"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="212">
+        <v>130100</v>
+      </c>
+      <c r="E53" s="137" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="102" t="s">
-        <v>116</v>
-      </c>
-      <c r="B53" s="98"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="147">
-        <v>105000</v>
-      </c>
-      <c r="E53" s="137" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="156" t="s">
-        <v>139</v>
-      </c>
-      <c r="B54" s="157"/>
+      <c r="G53" s="33"/>
+    </row>
+    <row r="54" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="214" t="s">
+        <v>140</v>
+      </c>
+      <c r="B54" s="215"/>
       <c r="C54" s="5"/>
-      <c r="D54" s="147">
-        <v>80700</v>
+      <c r="D54" s="212">
+        <v>16000</v>
       </c>
       <c r="E54" s="137" t="s">
+        <v>128</v>
+      </c>
+      <c r="G54" s="33"/>
+    </row>
+    <row r="55" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="161" t="s">
         <v>131</v>
       </c>
-      <c r="G54" s="33"/>
-    </row>
-    <row r="55" spans="1:7" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="156" t="s">
-        <v>130</v>
-      </c>
-      <c r="B55" s="157"/>
+      <c r="B55" s="162"/>
       <c r="C55" s="5"/>
-      <c r="D55" s="147">
-        <v>80700</v>
+      <c r="D55" s="146">
+        <v>666105</v>
       </c>
       <c r="E55" s="137" t="s">
-        <v>131</v>
-      </c>
-      <c r="G55" s="33"/>
-    </row>
-    <row r="56" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="156" t="s">
-        <v>134</v>
-      </c>
-      <c r="B56" s="157"/>
+        <v>124</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="102"/>
+      <c r="B56" s="98"/>
       <c r="C56" s="5"/>
-      <c r="D56" s="147">
-        <v>666105</v>
-      </c>
-      <c r="E56" s="137" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="102"/>
-      <c r="B57" s="98"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="147"/>
-      <c r="E57" s="136"/>
-    </row>
-    <row r="58" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="24" t="s">
+      <c r="D56" s="146"/>
+      <c r="E56" s="136"/>
+    </row>
+    <row r="57" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B58" s="27"/>
-      <c r="C58" s="27"/>
-      <c r="D58" s="26"/>
-      <c r="E58" s="150">
-        <f>SUM(D52:D57)</f>
-        <v>957646.2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="27" t="s">
+      <c r="B57" s="27"/>
+      <c r="C57" s="27"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="149">
+        <f>SUM(D51:D56)</f>
+        <v>942346.2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="B59" s="49"/>
-      <c r="C59" s="24"/>
-      <c r="D59" s="145"/>
-      <c r="E59" s="96"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B58" s="49"/>
+      <c r="C58" s="24"/>
+      <c r="D58" s="144"/>
+      <c r="E58" s="96"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B59" s="5"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="146">
+        <v>69000</v>
+      </c>
+      <c r="E59" s="97"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
-      <c r="D60" s="147">
-        <v>69000</v>
-      </c>
-      <c r="E60" s="97"/>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B61" s="5"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="147">
+      <c r="D60" s="146">
         <f>80429.95+2977</f>
         <v>83406.95</v>
       </c>
-      <c r="E61" s="31"/>
-    </row>
-    <row r="62" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="40" t="s">
+      <c r="E60" s="31"/>
+    </row>
+    <row r="61" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="B62" s="40"/>
-      <c r="C62" s="40"/>
-      <c r="D62" s="63"/>
-      <c r="E62" s="58">
-        <f>SUM(D60:D61)</f>
+      <c r="B61" s="40"/>
+      <c r="C61" s="40"/>
+      <c r="D61" s="63"/>
+      <c r="E61" s="58">
+        <f>SUM(D59:D60)</f>
         <v>152406.95000000001</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="5"/>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="57"/>
-      <c r="E63" s="64"/>
-    </row>
-    <row r="64" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="B64" s="25"/>
-      <c r="C64" s="25"/>
-      <c r="D64" s="65"/>
-      <c r="E64" s="66">
+    <row r="62" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="5"/>
+      <c r="B62" s="5"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="57"/>
+      <c r="E62" s="64"/>
+    </row>
+    <row r="63" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="B63" s="25"/>
+      <c r="C63" s="25"/>
+      <c r="D63" s="65"/>
+      <c r="E63" s="66">
         <f>4095718.96-3641704.21</f>
         <v>454014.75</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="1"/>
-      <c r="D65" s="67"/>
-      <c r="E65" s="68"/>
-      <c r="F65" s="33"/>
-    </row>
-    <row r="66" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="3" t="s">
+    <row r="64" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="1"/>
+      <c r="D64" s="67"/>
+      <c r="E64" s="68"/>
+      <c r="F64" s="33"/>
+    </row>
+    <row r="65" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B66" s="9"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="69"/>
-      <c r="E66" s="70">
-        <f>(SUM(E28:E64))</f>
-        <v>4095718.96</v>
-      </c>
-      <c r="F66" s="88"/>
-      <c r="G66" s="33"/>
+      <c r="B65" s="9"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="69"/>
+      <c r="E65" s="70">
+        <f>(SUM(E28:E63))</f>
+        <v>4885137.88</v>
+      </c>
+      <c r="F65" s="88"/>
+      <c r="G65" s="33"/>
+      <c r="H65" s="77"/>
+      <c r="I65" s="77"/>
+      <c r="J65" s="77"/>
+      <c r="K65" s="77"/>
+      <c r="L65" s="77"/>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="D66" s="67"/>
+      <c r="E66" s="67"/>
       <c r="H66" s="77"/>
       <c r="I66" s="77"/>
       <c r="J66" s="77"/>
       <c r="K66" s="77"/>
       <c r="L66" s="77"/>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D67" s="67"/>
       <c r="E67" s="67"/>
-      <c r="H67" s="77"/>
-      <c r="I67" s="77"/>
-      <c r="J67" s="77"/>
-      <c r="K67" s="77"/>
-      <c r="L67" s="77"/>
-    </row>
-    <row r="68" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D68" s="67"/>
-      <c r="E68" s="67"/>
-      <c r="H68" s="103"/>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A69" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B69" s="11"/>
-      <c r="C69" s="12"/>
-      <c r="D69" s="71"/>
-      <c r="E69" s="72"/>
-    </row>
-    <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="156"/>
-      <c r="B70" s="157"/>
+      <c r="H67" s="103"/>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A68" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B68" s="11"/>
+      <c r="C68" s="12"/>
+      <c r="D68" s="71"/>
+      <c r="E68" s="72"/>
+    </row>
+    <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="161"/>
+      <c r="B69" s="162"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="80"/>
+      <c r="E69" s="59"/>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A70" s="161"/>
+      <c r="B70" s="162"/>
       <c r="C70" s="5"/>
-      <c r="D70" s="80"/>
+      <c r="D70" s="61"/>
       <c r="E70" s="59"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A71" s="156"/>
-      <c r="B71" s="157"/>
+    <row r="71" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="165"/>
+      <c r="B71" s="166"/>
       <c r="C71" s="5"/>
       <c r="D71" s="61"/>
       <c r="E71" s="59"/>
     </row>
-    <row r="72" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="163"/>
-      <c r="B72" s="164"/>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A72" s="60"/>
+      <c r="B72" s="62"/>
       <c r="C72" s="5"/>
       <c r="D72" s="61"/>
       <c r="E72" s="59"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A73" s="60"/>
-      <c r="B73" s="62"/>
-      <c r="C73" s="5"/>
-      <c r="D73" s="61"/>
-      <c r="E73" s="59"/>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A74" s="38"/>
-      <c r="B74" s="37"/>
-      <c r="C74" s="37"/>
-      <c r="D74" s="45"/>
-      <c r="E74" s="45">
-        <f>SUM(D70:D73)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="76" spans="1:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="77" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="138" t="s">
-        <v>118</v>
-      </c>
-      <c r="B77" s="139"/>
-      <c r="C77" s="139"/>
-      <c r="D77" s="140"/>
-      <c r="E77" s="152">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A73" s="38"/>
+      <c r="B73" s="37"/>
+      <c r="C73" s="37"/>
+      <c r="D73" s="45"/>
+      <c r="E73" s="45">
+        <f>SUM(D69:D72)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="75" spans="1:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="76" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="138" t="s">
+        <v>117</v>
+      </c>
+      <c r="B76" s="139"/>
+      <c r="C76" s="139"/>
+      <c r="D76" s="140"/>
+      <c r="E76" s="151">
         <v>120000</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="79" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="3" t="s">
+    <row r="77" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="78" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B79" s="9"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="50">
-        <f>E74+E77</f>
+      <c r="B78" s="9"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="50">
+        <f>E73+E76</f>
         <v>120000</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="81" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="80" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="B80" s="56">
+        <f>E65</f>
+        <v>4885137.88</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="55" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B81" s="56">
-        <f>E66</f>
-        <v>4095718.96</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <f>E65-E63</f>
+        <v>4431123.13</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="55" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B82" s="56">
-        <f>E66-E64</f>
-        <v>3641704.21</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <f>E78-E76</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="55" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B83" s="56">
-        <f>E79-E77</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="55" t="s">
-        <v>33</v>
-      </c>
-      <c r="B84" s="56">
-        <f>E79</f>
+        <f>E78</f>
         <v>120000</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="81" t="s">
-        <v>107</v>
-      </c>
-      <c r="B87" s="82">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" s="81" t="s">
+        <v>106</v>
+      </c>
+      <c r="B86" s="82">
         <v>493837.39999999991</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="130" t="s">
-        <v>111</v>
-      </c>
-      <c r="B88" s="131">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" s="130" t="s">
+        <v>110</v>
+      </c>
+      <c r="B87" s="131">
         <f>PRORRATEO!G38</f>
         <v>400000</v>
+      </c>
+      <c r="C87" s="22"/>
+      <c r="D87" s="33"/>
+      <c r="E87" s="78"/>
+      <c r="F87" s="79"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" s="153" t="s">
+        <v>133</v>
+      </c>
+      <c r="B88" s="152">
+        <v>-27200</v>
       </c>
       <c r="C88" s="22"/>
       <c r="D88" s="33"/>
       <c r="E88" s="78"/>
       <c r="F88" s="79"/>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="154" t="s">
-        <v>136</v>
-      </c>
-      <c r="B89" s="153">
-        <v>-27200</v>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" s="153" t="s">
+        <v>134</v>
+      </c>
+      <c r="B89" s="152">
+        <v>-11452.78</v>
       </c>
       <c r="C89" s="22"/>
       <c r="D89" s="33"/>
       <c r="E89" s="78"/>
       <c r="F89" s="79"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="154" t="s">
-        <v>137</v>
-      </c>
-      <c r="B90" s="153">
-        <v>-11452.78</v>
+        <v>135</v>
+      </c>
+      <c r="B90" s="152">
+        <v>-120000</v>
       </c>
       <c r="C90" s="22"/>
       <c r="D90" s="33"/>
       <c r="E90" s="78"/>
       <c r="F90" s="79"/>
     </row>
-    <row r="91" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="155" t="s">
-        <v>138</v>
-      </c>
-      <c r="B91" s="153">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" s="150" t="s">
+        <v>132</v>
+      </c>
+      <c r="B91" s="152">
         <v>-120000</v>
       </c>
       <c r="C91" s="22"/>
@@ -2833,181 +2814,169 @@
       <c r="E91" s="78"/>
       <c r="F91" s="79"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="151" t="s">
-        <v>135</v>
-      </c>
-      <c r="B92" s="153">
-        <v>-120000</v>
+    <row r="92" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="132" t="s">
+        <v>37</v>
+      </c>
+      <c r="B92" s="133">
+        <f>SUM(B86:C91)</f>
+        <v>615184.61999999988</v>
       </c>
       <c r="C92" s="22"/>
-      <c r="D92" s="33"/>
-      <c r="E92" s="78"/>
-      <c r="F92" s="79"/>
-    </row>
-    <row r="93" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="132" t="s">
-        <v>38</v>
-      </c>
-      <c r="B93" s="133">
-        <f>SUM(B87:C92)</f>
-        <v>615184.61999999988</v>
-      </c>
-      <c r="C93" s="22"/>
-    </row>
-    <row r="94" spans="1:6" s="30" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A94"/>
-      <c r="B94" s="32"/>
+    </row>
+    <row r="93" spans="1:6" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A93"/>
+      <c r="B93" s="32"/>
+      <c r="C93" s="29"/>
+    </row>
+    <row r="94" spans="1:6" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="81" t="s">
+        <v>43</v>
+      </c>
+      <c r="B94" s="82">
+        <v>1300550.2430000012</v>
+      </c>
       <c r="C94" s="29"/>
-    </row>
-    <row r="95" spans="1:6" s="30" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="81" t="s">
-        <v>44</v>
-      </c>
-      <c r="B95" s="82">
-        <v>1300550.2430000012</v>
-      </c>
-      <c r="C95" s="29"/>
-      <c r="D95" s="36"/>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D94" s="36"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" s="42" t="s">
+        <v>39</v>
+      </c>
+      <c r="B95" s="86">
+        <f>-B81</f>
+        <v>-4431123.13</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="42" t="s">
         <v>40</v>
       </c>
       <c r="B96" s="86">
         <f>-B82</f>
-        <v>-3641704.21</v>
-      </c>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" s="42" t="s">
+        <v>42</v>
+      </c>
+      <c r="B97" s="86">
+        <f>B106</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A98" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="B97" s="86">
-        <f>-B83</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A98" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="B98" s="86">
-        <f>B107</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A99" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="B99" s="87">
+      <c r="B98" s="87">
         <f>PRORRATEO!G37</f>
         <v>3916704.6200000006</v>
       </c>
     </row>
-    <row r="100" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="84" t="s">
-        <v>38</v>
-      </c>
-      <c r="B100" s="85">
-        <f>SUM(B95:C99)</f>
-        <v>1575550.6530000018</v>
-      </c>
-      <c r="D100" s="32"/>
-      <c r="E100" s="33"/>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A101" s="83"/>
-      <c r="B101" s="83"/>
-    </row>
-    <row r="102" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A103" s="162" t="s">
+    <row r="99" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="84" t="s">
+        <v>37</v>
+      </c>
+      <c r="B99" s="85">
+        <f>SUM(B94:C98)</f>
+        <v>786131.73300000187</v>
+      </c>
+      <c r="D99" s="32"/>
+      <c r="E99" s="33"/>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A100" s="83"/>
+      <c r="B100" s="83"/>
+    </row>
+    <row r="101" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A102" s="164" t="s">
         <v>26</v>
       </c>
-      <c r="B103" s="162"/>
-      <c r="C103" s="162"/>
-    </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A104" s="162"/>
-      <c r="B104" s="162"/>
-      <c r="C104" s="162"/>
-    </row>
-    <row r="105" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B102" s="164"/>
+      <c r="C102" s="164"/>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A103" s="164"/>
+      <c r="B103" s="164"/>
+      <c r="C103" s="164"/>
+    </row>
+    <row r="104" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="74"/>
+      <c r="B104" s="28"/>
+      <c r="C104" s="28">
+        <v>40000</v>
+      </c>
+      <c r="E104" s="88"/>
+    </row>
+    <row r="105" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="74"/>
-      <c r="B105" s="28"/>
-      <c r="C105" s="28">
-        <v>40000</v>
-      </c>
-      <c r="E105" s="88"/>
-    </row>
-    <row r="106" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="74"/>
-      <c r="B106" s="76"/>
-      <c r="C106" s="73"/>
-      <c r="D106" s="88"/>
-    </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A107" s="34" t="s">
+      <c r="B105" s="76"/>
+      <c r="C105" s="73"/>
+      <c r="D105" s="88"/>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A106" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="B107" s="75">
-        <f>SUM(B105:B106)</f>
-        <v>0</v>
-      </c>
-      <c r="C107" s="35"/>
-    </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M108" s="7"/>
-    </row>
-    <row r="109" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="161"/>
-      <c r="B109" s="161"/>
-      <c r="C109" s="161"/>
-      <c r="D109" s="161"/>
-      <c r="E109" s="161"/>
-    </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A110" s="161"/>
-      <c r="B110" s="161"/>
-      <c r="C110" s="161"/>
-      <c r="D110" s="161"/>
-      <c r="E110" s="161"/>
-    </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A111" s="161"/>
-      <c r="B111" s="161"/>
-      <c r="C111" s="161"/>
-      <c r="D111" s="161"/>
-      <c r="E111" s="161"/>
-    </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A112" s="161"/>
-      <c r="B112" s="161"/>
-      <c r="C112" s="161"/>
-      <c r="D112" s="161"/>
-      <c r="E112" s="161"/>
+      <c r="B106" s="75">
+        <f>SUM(B104:B105)</f>
+        <v>0</v>
+      </c>
+      <c r="C106" s="35"/>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M107" s="7"/>
+    </row>
+    <row r="108" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="163"/>
+      <c r="B108" s="163"/>
+      <c r="C108" s="163"/>
+      <c r="D108" s="163"/>
+      <c r="E108" s="163"/>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A109" s="163"/>
+      <c r="B109" s="163"/>
+      <c r="C109" s="163"/>
+      <c r="D109" s="163"/>
+      <c r="E109" s="163"/>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A110" s="163"/>
+      <c r="B110" s="163"/>
+      <c r="C110" s="163"/>
+      <c r="D110" s="163"/>
+      <c r="E110" s="163"/>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A111" s="163"/>
+      <c r="B111" s="163"/>
+      <c r="C111" s="163"/>
+      <c r="D111" s="163"/>
+      <c r="E111" s="163"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A109:E112"/>
-    <mergeCell ref="A103:C104"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A55:B55"/>
     <mergeCell ref="A54:B54"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="E37:E38"/>
     <mergeCell ref="B1:D1"/>
-    <mergeCell ref="A35:B35"/>
     <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A33:B33"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A38:B39"/>
+    <mergeCell ref="A37:B38"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A108:E111"/>
+    <mergeCell ref="A102:C103"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A71:B71"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3018,73 +2987,73 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="6.5703125" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" customWidth="1"/>
-    <col min="4" max="4" width="22.28515625" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" customWidth="1"/>
-    <col min="6" max="7" width="14.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="6.5546875" customWidth="1"/>
+    <col min="3" max="3" width="20.44140625" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.44140625" customWidth="1"/>
+    <col min="6" max="7" width="14.109375" customWidth="1"/>
     <col min="8" max="8" width="14" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="10.5703125" customWidth="1"/>
-    <col min="10" max="11" width="9.5703125" customWidth="1"/>
-    <col min="12" max="13" width="12.42578125" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" customWidth="1"/>
-    <col min="16" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5546875" customWidth="1"/>
+    <col min="10" max="11" width="9.5546875" customWidth="1"/>
+    <col min="12" max="13" width="12.44140625" customWidth="1"/>
+    <col min="14" max="14" width="14.6640625" customWidth="1"/>
+    <col min="15" max="15" width="14.33203125" customWidth="1"/>
+    <col min="16" max="16" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
-      <c r="E1" s="186"/>
-      <c r="F1" s="186"/>
-      <c r="G1" s="186"/>
-      <c r="H1" s="186"/>
-      <c r="I1" s="186"/>
-      <c r="J1" s="186"/>
-      <c r="K1" s="186"/>
-      <c r="L1" s="186"/>
-      <c r="M1" s="186"/>
-      <c r="N1" s="186"/>
+      <c r="E1" s="180"/>
+      <c r="F1" s="180"/>
+      <c r="G1" s="180"/>
+      <c r="H1" s="180"/>
+      <c r="I1" s="180"/>
+      <c r="J1" s="180"/>
+      <c r="K1" s="180"/>
+      <c r="L1" s="180"/>
+      <c r="M1" s="180"/>
+      <c r="N1" s="180"/>
       <c r="O1" s="6"/>
     </row>
-    <row r="2" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="177">
-        <v>0</v>
-      </c>
-      <c r="E2" s="177"/>
+        <v>47</v>
+      </c>
+      <c r="D2" s="206">
+        <v>0</v>
+      </c>
+      <c r="E2" s="206"/>
       <c r="F2" s="6"/>
-      <c r="G2" s="177"/>
-      <c r="H2" s="177"/>
-      <c r="I2" s="177"/>
+      <c r="G2" s="206"/>
+      <c r="H2" s="206"/>
+      <c r="I2" s="206"/>
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="L2" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="M2" s="176">
+        <v>104</v>
+      </c>
+      <c r="M2" s="205">
         <f>Q2</f>
         <v>4095718.96</v>
       </c>
-      <c r="N2" s="176"/>
+      <c r="N2" s="205"/>
       <c r="O2" s="43"/>
       <c r="P2" s="21"/>
       <c r="Q2">
         <v>4095718.96</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -3101,168 +3070,168 @@
       <c r="N3" s="46"/>
       <c r="O3" s="46"/>
     </row>
-    <row r="4" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="192" t="str">
+    <row r="4" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="189" t="str">
         <f>RESUMEN!A13</f>
         <v>Importante para dueños o inquilinos de departamentos o coheras: Queremos recordarles una cuestión importante respecto a los pagos de expensas que ayuda a evitar errores en la imputación de los mismos. El sistema que utilizamos asigna centavos únicos a cada Unidad Funcional (UF), lo cual nos permite identificar automáticamente a qué unidad corresponde cada transferencia. Es decir, cada UF tiene un número específico de centavos que actúa como "identificador". Por ejemplo, si tu UF es la 45, el importe a abonar debería terminar en $...,45. Si tenés más de una unidad (por ejemplo, un departamento y una cochera), cada una tiene su propio código de centavos. En esos casos, te pedimos por favor que realices una transferencia por cada UF, respetando el importe con sus centavos correspondientes. Sabemos que a veces por comodidad se suele enviar todo junto en una sola transferencia, pero esto puede generar confusión o errores en la imputación automática. Realizar los pagos por separado nos permite asegurar que cada importe se asigne correctamente. Agradecemos muchísimo la colaboración para seguir manteniendo todo ordenado. Saludos cordiales.</v>
       </c>
-      <c r="B4" s="193"/>
-      <c r="C4" s="193"/>
-      <c r="D4" s="193"/>
-      <c r="E4" s="193"/>
-      <c r="F4" s="193"/>
-      <c r="G4" s="193"/>
-      <c r="H4" s="193"/>
-      <c r="I4" s="193"/>
-      <c r="J4" s="193"/>
-      <c r="K4" s="193"/>
-      <c r="L4" s="193"/>
-      <c r="M4" s="193"/>
-      <c r="N4" s="193"/>
-      <c r="O4" s="194"/>
-    </row>
-    <row r="5" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="195"/>
-      <c r="B5" s="196"/>
-      <c r="C5" s="196"/>
-      <c r="D5" s="196"/>
-      <c r="E5" s="196"/>
-      <c r="F5" s="196"/>
-      <c r="G5" s="196"/>
-      <c r="H5" s="196"/>
-      <c r="I5" s="196"/>
-      <c r="J5" s="196"/>
-      <c r="K5" s="196"/>
-      <c r="L5" s="196"/>
-      <c r="M5" s="196"/>
-      <c r="N5" s="196"/>
-      <c r="O5" s="197"/>
-    </row>
-    <row r="6" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="195"/>
-      <c r="B6" s="196"/>
-      <c r="C6" s="196"/>
-      <c r="D6" s="196"/>
-      <c r="E6" s="196"/>
-      <c r="F6" s="196"/>
-      <c r="G6" s="196"/>
-      <c r="H6" s="196"/>
-      <c r="I6" s="196"/>
-      <c r="J6" s="196"/>
-      <c r="K6" s="196"/>
-      <c r="L6" s="196"/>
-      <c r="M6" s="196"/>
-      <c r="N6" s="196"/>
-      <c r="O6" s="197"/>
-    </row>
-    <row r="7" spans="1:18" ht="64.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="195"/>
-      <c r="B7" s="196"/>
-      <c r="C7" s="196"/>
-      <c r="D7" s="196"/>
-      <c r="E7" s="196"/>
-      <c r="F7" s="196"/>
-      <c r="G7" s="196"/>
-      <c r="H7" s="196"/>
-      <c r="I7" s="196"/>
-      <c r="J7" s="196"/>
-      <c r="K7" s="196"/>
-      <c r="L7" s="196"/>
-      <c r="M7" s="196"/>
-      <c r="N7" s="196"/>
-      <c r="O7" s="197"/>
-    </row>
-    <row r="8" spans="1:18" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="198"/>
-      <c r="B8" s="199"/>
-      <c r="C8" s="199"/>
-      <c r="D8" s="199"/>
-      <c r="E8" s="199"/>
-      <c r="F8" s="199"/>
-      <c r="G8" s="199"/>
-      <c r="H8" s="199"/>
-      <c r="I8" s="199"/>
-      <c r="J8" s="199"/>
-      <c r="K8" s="199"/>
-      <c r="L8" s="199"/>
-      <c r="M8" s="199"/>
-      <c r="N8" s="199"/>
-      <c r="O8" s="200"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" s="184" t="s">
+      <c r="B4" s="190"/>
+      <c r="C4" s="190"/>
+      <c r="D4" s="190"/>
+      <c r="E4" s="190"/>
+      <c r="F4" s="190"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="190"/>
+      <c r="I4" s="190"/>
+      <c r="J4" s="190"/>
+      <c r="K4" s="190"/>
+      <c r="L4" s="190"/>
+      <c r="M4" s="190"/>
+      <c r="N4" s="190"/>
+      <c r="O4" s="191"/>
+    </row>
+    <row r="5" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="192"/>
+      <c r="B5" s="193"/>
+      <c r="C5" s="193"/>
+      <c r="D5" s="193"/>
+      <c r="E5" s="193"/>
+      <c r="F5" s="193"/>
+      <c r="G5" s="193"/>
+      <c r="H5" s="193"/>
+      <c r="I5" s="193"/>
+      <c r="J5" s="193"/>
+      <c r="K5" s="193"/>
+      <c r="L5" s="193"/>
+      <c r="M5" s="193"/>
+      <c r="N5" s="193"/>
+      <c r="O5" s="194"/>
+    </row>
+    <row r="6" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="192"/>
+      <c r="B6" s="193"/>
+      <c r="C6" s="193"/>
+      <c r="D6" s="193"/>
+      <c r="E6" s="193"/>
+      <c r="F6" s="193"/>
+      <c r="G6" s="193"/>
+      <c r="H6" s="193"/>
+      <c r="I6" s="193"/>
+      <c r="J6" s="193"/>
+      <c r="K6" s="193"/>
+      <c r="L6" s="193"/>
+      <c r="M6" s="193"/>
+      <c r="N6" s="193"/>
+      <c r="O6" s="194"/>
+    </row>
+    <row r="7" spans="1:18" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="192"/>
+      <c r="B7" s="193"/>
+      <c r="C7" s="193"/>
+      <c r="D7" s="193"/>
+      <c r="E7" s="193"/>
+      <c r="F7" s="193"/>
+      <c r="G7" s="193"/>
+      <c r="H7" s="193"/>
+      <c r="I7" s="193"/>
+      <c r="J7" s="193"/>
+      <c r="K7" s="193"/>
+      <c r="L7" s="193"/>
+      <c r="M7" s="193"/>
+      <c r="N7" s="193"/>
+      <c r="O7" s="194"/>
+    </row>
+    <row r="8" spans="1:18" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="195"/>
+      <c r="B8" s="196"/>
+      <c r="C8" s="196"/>
+      <c r="D8" s="196"/>
+      <c r="E8" s="196"/>
+      <c r="F8" s="196"/>
+      <c r="G8" s="196"/>
+      <c r="H8" s="196"/>
+      <c r="I8" s="196"/>
+      <c r="J8" s="196"/>
+      <c r="K8" s="196"/>
+      <c r="L8" s="196"/>
+      <c r="M8" s="196"/>
+      <c r="N8" s="196"/>
+      <c r="O8" s="197"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9" s="181" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="178" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" s="178" t="s">
+      <c r="B9" s="183" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="183" t="s">
         <v>6</v>
       </c>
       <c r="D9" s="125"/>
-      <c r="E9" s="178" t="s">
+      <c r="E9" s="183" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="184" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="178" t="s">
+      <c r="F9" s="181" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="183" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="178" t="s">
-        <v>109</v>
-      </c>
-      <c r="I9" s="188" t="s">
+      <c r="H9" s="183" t="s">
+        <v>108</v>
+      </c>
+      <c r="I9" s="185" t="s">
         <v>24</v>
       </c>
-      <c r="J9" s="184" t="s">
-        <v>34</v>
-      </c>
-      <c r="K9" s="184" t="s">
-        <v>115</v>
-      </c>
-      <c r="L9" s="184" t="s">
+      <c r="J9" s="181" t="s">
+        <v>33</v>
+      </c>
+      <c r="K9" s="181" t="s">
+        <v>114</v>
+      </c>
+      <c r="L9" s="181" t="s">
         <v>21</v>
       </c>
-      <c r="M9" s="190" t="s">
-        <v>49</v>
+      <c r="M9" s="187" t="s">
+        <v>48</v>
       </c>
       <c r="N9" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="O9" s="202" t="s">
+      <c r="O9" s="200" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="201"/>
-      <c r="B10" s="179"/>
-      <c r="C10" s="187"/>
+    <row r="10" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="198"/>
+      <c r="B10" s="199"/>
+      <c r="C10" s="184"/>
       <c r="D10" s="126"/>
-      <c r="E10" s="187"/>
-      <c r="F10" s="185"/>
-      <c r="G10" s="187"/>
-      <c r="H10" s="179"/>
-      <c r="I10" s="189"/>
-      <c r="J10" s="185"/>
-      <c r="K10" s="185"/>
-      <c r="L10" s="185"/>
-      <c r="M10" s="191"/>
+      <c r="E10" s="184"/>
+      <c r="F10" s="182"/>
+      <c r="G10" s="184"/>
+      <c r="H10" s="199"/>
+      <c r="I10" s="186"/>
+      <c r="J10" s="182"/>
+      <c r="K10" s="182"/>
+      <c r="L10" s="182"/>
+      <c r="M10" s="188"/>
       <c r="N10" s="47" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 18/06</v>
       </c>
-      <c r="O10" s="203"/>
-    </row>
-    <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O10" s="201"/>
+    </row>
+    <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="104" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="104" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="104" t="s">
+      <c r="C11" s="104" t="s">
         <v>53</v>
-      </c>
-      <c r="C11" s="104" t="s">
-        <v>54</v>
       </c>
       <c r="D11" s="104"/>
       <c r="E11" s="123">
@@ -3271,12 +3240,12 @@
       <c r="F11" s="106">
         <v>260531.01</v>
       </c>
-      <c r="G11" s="204">
+      <c r="G11" s="155">
         <f>F11</f>
         <v>260531.01</v>
       </c>
       <c r="H11" s="107" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I11" s="108">
         <f t="shared" ref="I11:I35" si="0">F11-G11</f>
@@ -3308,18 +3277,18 @@
       </c>
       <c r="Q11" s="33"/>
     </row>
-    <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="104" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B12" s="104" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="104" t="s">
-        <v>56</v>
-      </c>
       <c r="D12" s="104" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E12" s="123">
         <v>4.33</v>
@@ -3331,7 +3300,7 @@
         <v>182377.02</v>
       </c>
       <c r="H12" s="107" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I12" s="108">
         <f t="shared" si="0"/>
@@ -3364,15 +3333,15 @@
       </c>
       <c r="Q12" s="33"/>
     </row>
-    <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="113" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="113" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="113" t="s">
         <v>57</v>
-      </c>
-      <c r="B13" s="113" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="113" t="s">
-        <v>58</v>
       </c>
       <c r="D13" s="113"/>
       <c r="E13" s="124">
@@ -3385,7 +3354,7 @@
         <v>250000.03</v>
       </c>
       <c r="H13" s="107" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I13" s="108">
         <f t="shared" si="0"/>
@@ -3418,15 +3387,15 @@
       </c>
       <c r="Q13" s="32"/>
     </row>
-    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="104" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B14" s="104" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C14" s="104" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D14" s="104"/>
       <c r="E14" s="123">
@@ -3439,7 +3408,7 @@
         <v>188017.04</v>
       </c>
       <c r="H14" s="107" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I14" s="108">
         <f t="shared" si="0"/>
@@ -3472,18 +3441,18 @@
       </c>
       <c r="R14" s="33"/>
     </row>
-    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="104" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="104" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="104" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="104" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" s="104" t="s">
-        <v>61</v>
-      </c>
       <c r="D15" s="104" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E15" s="123">
         <v>6.18</v>
@@ -3496,7 +3465,7 @@
         <v>268170.05</v>
       </c>
       <c r="H15" s="107" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I15" s="108">
         <f t="shared" si="0"/>
@@ -3529,15 +3498,15 @@
       </c>
       <c r="R15" s="33"/>
     </row>
-    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="104" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B16" s="104" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C16" s="104" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D16" s="104"/>
       <c r="E16" s="123">
@@ -3550,7 +3519,7 @@
         <v>182529.06</v>
       </c>
       <c r="H16" s="107" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I16" s="108">
         <f t="shared" si="0"/>
@@ -3582,15 +3551,15 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="104" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="104" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="104" t="s">
         <v>63</v>
-      </c>
-      <c r="B17" s="104" t="s">
-        <v>53</v>
-      </c>
-      <c r="C17" s="104" t="s">
-        <v>64</v>
       </c>
       <c r="D17" s="104"/>
       <c r="E17" s="123">
@@ -3604,7 +3573,7 @@
         <v>278411.78000000003</v>
       </c>
       <c r="H17" s="107" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I17" s="108">
         <f t="shared" si="0"/>
@@ -3636,15 +3605,15 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="104" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B18" s="104" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C18" s="104" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" s="104"/>
       <c r="E18" s="123">
@@ -3658,7 +3627,7 @@
         <v>177213.08</v>
       </c>
       <c r="H18" s="107" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I18" s="108">
         <f t="shared" si="0"/>
@@ -3690,15 +3659,15 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="104" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" s="104" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="104" t="s">
         <v>66</v>
-      </c>
-      <c r="B19" s="104" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="104" t="s">
-        <v>67</v>
       </c>
       <c r="D19" s="104"/>
       <c r="E19" s="123">
@@ -3712,7 +3681,7 @@
         <v>367411.78</v>
       </c>
       <c r="H19" s="107" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I19" s="108">
         <f t="shared" si="0"/>
@@ -3747,15 +3716,15 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="104" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B20" s="104" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C20" s="104" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D20" s="104"/>
       <c r="E20" s="123">
@@ -3768,7 +3737,7 @@
         <v>176552</v>
       </c>
       <c r="H20" s="107" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I20" s="108">
         <f t="shared" si="0"/>
@@ -3800,18 +3769,18 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="104" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="104" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="104" t="s">
         <v>69</v>
       </c>
-      <c r="B21" s="104" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="104" t="s">
-        <v>70</v>
-      </c>
       <c r="D21" s="104" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E21" s="123">
         <v>6.18</v>
@@ -3819,12 +3788,12 @@
       <c r="F21" s="106">
         <v>252926.11</v>
       </c>
-      <c r="G21" s="204">
+      <c r="G21" s="155">
         <f>F21</f>
         <v>252926.11</v>
       </c>
       <c r="H21" s="107" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I21" s="108">
         <f t="shared" si="0"/>
@@ -3856,15 +3825,15 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="104" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B22" s="104" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C22" s="104" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D22" s="104"/>
       <c r="E22" s="123">
@@ -3877,7 +3846,7 @@
         <v>181407</v>
       </c>
       <c r="H22" s="107" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I22" s="108">
         <f t="shared" si="0"/>
@@ -3909,18 +3878,18 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="104" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" s="104" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="104" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="104" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" s="104" t="s">
-        <v>73</v>
-      </c>
       <c r="D23" s="104" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E23" s="123">
         <v>6.18</v>
@@ -3933,7 +3902,7 @@
         <v>260531.13</v>
       </c>
       <c r="H23" s="107" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I23" s="108">
         <f t="shared" si="0"/>
@@ -3965,15 +3934,15 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="104" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B24" s="104" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C24" s="104" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D24" s="104"/>
       <c r="E24" s="123">
@@ -3987,7 +3956,7 @@
         <v>182541.14</v>
       </c>
       <c r="H24" s="107" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I24" s="108">
         <f t="shared" si="0"/>
@@ -4019,15 +3988,15 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="113" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" s="113" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="113" t="s">
         <v>75</v>
-      </c>
-      <c r="B25" s="113" t="s">
-        <v>53</v>
-      </c>
-      <c r="C25" s="113" t="s">
-        <v>76</v>
       </c>
       <c r="D25" s="113"/>
       <c r="E25" s="124">
@@ -4041,7 +4010,7 @@
         <v>258531.58999999997</v>
       </c>
       <c r="H25" s="107" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I25" s="108">
         <f t="shared" si="0"/>
@@ -4073,15 +4042,15 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="104" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" s="104" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="104" t="s">
         <v>75</v>
-      </c>
-      <c r="B26" s="104" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26" s="104" t="s">
-        <v>76</v>
       </c>
       <c r="D26" s="104"/>
       <c r="E26" s="123">
@@ -4095,7 +4064,7 @@
         <v>182541.16</v>
       </c>
       <c r="H26" s="107" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I26" s="108">
         <f t="shared" si="0"/>
@@ -4127,18 +4096,18 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="104" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27" s="104" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="104" t="s">
         <v>77</v>
       </c>
-      <c r="B27" s="104" t="s">
-        <v>53</v>
-      </c>
-      <c r="C27" s="104" t="s">
-        <v>78</v>
-      </c>
       <c r="D27" s="104" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E27" s="123">
         <v>6.18</v>
@@ -4151,7 +4120,7 @@
         <v>260531.17</v>
       </c>
       <c r="H27" s="107" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I27" s="108">
         <f t="shared" si="0"/>
@@ -4183,15 +4152,15 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="104" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B28" s="104" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C28" s="104" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D28" s="104"/>
       <c r="E28" s="123">
@@ -4200,12 +4169,12 @@
       <c r="F28" s="106">
         <v>182541.18</v>
       </c>
-      <c r="G28" s="204">
+      <c r="G28" s="155">
         <f>F28</f>
         <v>182541.18</v>
       </c>
       <c r="H28" s="107" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I28" s="108">
         <f t="shared" si="0"/>
@@ -4237,13 +4206,13 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="180" t="s">
-        <v>81</v>
-      </c>
-      <c r="B29" s="181"/>
+    <row r="29" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="207" t="s">
+        <v>80</v>
+      </c>
+      <c r="B29" s="208"/>
       <c r="C29" s="104" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D29" s="104"/>
       <c r="E29" s="123">
@@ -4257,7 +4226,7 @@
         <v>32588.19</v>
       </c>
       <c r="H29" s="107" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I29" s="108">
         <f t="shared" si="0"/>
@@ -4289,13 +4258,13 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="180" t="s">
-        <v>82</v>
-      </c>
-      <c r="B30" s="181"/>
+    <row r="30" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="207" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" s="208"/>
       <c r="C30" s="113" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D30" s="104"/>
       <c r="E30" s="123">
@@ -4304,11 +4273,11 @@
       <c r="F30" s="115">
         <v>24550.2</v>
       </c>
-      <c r="G30" s="204">
+      <c r="G30" s="155">
         <v>25000.2</v>
       </c>
       <c r="H30" s="107" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I30" s="108">
         <f t="shared" si="0"/>
@@ -4340,16 +4309,16 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="180" t="s">
-        <v>83</v>
-      </c>
-      <c r="B31" s="181"/>
+    <row r="31" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="207" t="s">
+        <v>82</v>
+      </c>
+      <c r="B31" s="208"/>
       <c r="C31" s="116" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D31" s="104" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E31" s="123">
         <v>0.77300000000000002</v>
@@ -4357,11 +4326,11 @@
       <c r="F31" s="115">
         <v>32588.21</v>
       </c>
-      <c r="G31" s="204">
+      <c r="G31" s="155">
         <v>35588.21</v>
       </c>
       <c r="H31" s="107" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I31" s="108">
         <f t="shared" si="0"/>
@@ -4393,13 +4362,13 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="180" t="s">
-        <v>84</v>
-      </c>
-      <c r="B32" s="181"/>
+    <row r="32" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="207" t="s">
+        <v>83</v>
+      </c>
+      <c r="B32" s="208"/>
       <c r="C32" s="104" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D32" s="104"/>
       <c r="E32" s="123">
@@ -4408,12 +4377,12 @@
       <c r="F32" s="115">
         <v>32588.22</v>
       </c>
-      <c r="G32" s="204">
+      <c r="G32" s="155">
         <f t="shared" ref="G32" si="7">F32</f>
         <v>32588.22</v>
       </c>
       <c r="H32" s="107" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I32" s="108">
         <f t="shared" si="0"/>
@@ -4445,13 +4414,13 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="180" t="s">
-        <v>85</v>
-      </c>
-      <c r="B33" s="181"/>
+    <row r="33" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="207" t="s">
+        <v>84</v>
+      </c>
+      <c r="B33" s="208"/>
       <c r="C33" s="117" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D33" s="117"/>
       <c r="E33" s="123">
@@ -4460,12 +4429,12 @@
       <c r="F33" s="115">
         <v>31610.23</v>
       </c>
-      <c r="G33" s="204">
+      <c r="G33" s="155">
         <f>G32</f>
         <v>32588.22</v>
       </c>
       <c r="H33" s="107" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I33" s="108">
         <f t="shared" si="0"/>
@@ -4497,16 +4466,16 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="180" t="s">
-        <v>86</v>
-      </c>
-      <c r="B34" s="181"/>
+    <row r="34" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="207" t="s">
+        <v>85</v>
+      </c>
+      <c r="B34" s="208"/>
       <c r="C34" s="117" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D34" s="117" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E34" s="123">
         <v>0.77300000000000002</v>
@@ -4514,11 +4483,11 @@
       <c r="F34" s="115">
         <v>31675.24</v>
       </c>
-      <c r="G34" s="204">
+      <c r="G34" s="155">
         <v>33000</v>
       </c>
       <c r="H34" s="107" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I34" s="108">
         <f t="shared" si="0"/>
@@ -4550,13 +4519,13 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="180" t="s">
-        <v>87</v>
-      </c>
-      <c r="B35" s="181"/>
+    <row r="35" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="207" t="s">
+        <v>86</v>
+      </c>
+      <c r="B35" s="208"/>
       <c r="C35" s="117" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D35" s="117"/>
       <c r="E35" s="105">
@@ -4570,7 +4539,7 @@
         <v>32588.25</v>
       </c>
       <c r="H35" s="107" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I35" s="108">
         <f t="shared" si="0"/>
@@ -4602,12 +4571,12 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="182" t="s">
-        <v>51</v>
-      </c>
-      <c r="B36" s="182"/>
-      <c r="C36" s="183"/>
+    <row r="36" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="209" t="s">
+        <v>50</v>
+      </c>
+      <c r="B36" s="209"/>
+      <c r="C36" s="210"/>
       <c r="D36" s="127"/>
       <c r="E36" s="118">
         <f t="shared" ref="E36:M36" si="8">SUM(E11:E35)</f>
@@ -4648,56 +4617,56 @@
         <v>4277121.2500000009</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C37" s="39"/>
       <c r="D37" s="39"/>
       <c r="F37" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G37" s="134">
         <f>SUMIF(H11:H35,"B",G11:G35)</f>
         <v>3916704.6200000006</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" s="173"/>
-      <c r="B38" s="173"/>
-      <c r="E38" s="174"/>
-      <c r="F38" s="175" t="s">
-        <v>113</v>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A38" s="202"/>
+      <c r="B38" s="202"/>
+      <c r="E38" s="203"/>
+      <c r="F38" s="204" t="s">
+        <v>112</v>
       </c>
       <c r="G38" s="134">
         <f>SUMIF(H11:H35,"E",G11:G35)</f>
         <v>400000</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" s="173"/>
-      <c r="B39" s="173"/>
-      <c r="E39" s="174"/>
-      <c r="F39" s="175"/>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A39" s="202"/>
+      <c r="B39" s="202"/>
+      <c r="E39" s="203"/>
+      <c r="F39" s="204"/>
       <c r="G39" s="135">
         <f>SUM(G37:G38)</f>
         <v>4316704.620000001</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F50">
         <f>SUM(E48:E49)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F54">
         <f>SUM(E52:E53)</f>
         <v>0</v>
@@ -4705,19 +4674,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="E1:N1"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="M9:M10"/>
-    <mergeCell ref="A4:O8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="O9:O10"/>
     <mergeCell ref="A38:B39"/>
     <mergeCell ref="E38:E39"/>
     <mergeCell ref="F38:F39"/>
@@ -4734,6 +4690,19 @@
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="K9:K10"/>
+    <mergeCell ref="E1:N1"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="A4:O8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="O9:O10"/>
   </mergeCells>
   <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4744,7 +4713,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
